--- a/docs/launch-wbs.xlsx
+++ b/docs/launch-wbs.xlsx
@@ -40,12 +40,12 @@
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
+      <color rgb="00F01A1A"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="00F01A1A"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -63,7 +63,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00Fde68A"/>
+        <fgColor rgb="00FDE68A"/>
       </patternFill>
     </fill>
     <fill>
@@ -113,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -137,21 +137,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -519,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -527,7 +518,7 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -675,7 +666,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Render 오토디플로이·브랜치 확인 + 멤버 초대(or FCM 등록)</t>
+          <t>Render 오토디플로이 확인·멤버 초대 · TourAPI 키 계정 확인</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -708,12 +699,12 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>TourAPI 키 발급 계정 = 제출용 키 일치 확인</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>하민</t>
+          <t>실서버 연결 빌드 정상 동작 확인 (로컬로그인)</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>규희</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -723,12 +714,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>8/16</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>키·계정 확인</t>
+          <t>운영 APK 로그인 OK</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -741,7 +732,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>실서버 연결 빌드 정상 동작 확인 (로컬로그인)</t>
+          <t>키 투입 + AAB 빌드 → 하민 전달</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -751,17 +742,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>8/15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8/16</t>
+          <t>8/17</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>운영 APK 로그인 OK</t>
+          <t>서명 AAB 파일</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
@@ -774,7 +765,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>소셜·Supabase 키 투입 + AAB 빌드</t>
+          <t>리스팅·이미지·설문 답안 전달 (준비 완료분)</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -789,12 +780,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>8/16</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>서명 AAB</t>
+          <t>자료 전달</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -807,17 +798,17 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Play 콘솔 세팅 (리스팅·이미지·설문 4종)</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>규희</t>
+          <t>(콘솔) 리스팅·설문 입력 + FCM env 등록</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>하민</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>8/16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -873,7 +864,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>공모전 제출물 목록·양식 파악 / 일러스트 지역 리스트업</t>
+          <t>공모전 제출물 목록·양식 파악 / 일러스트 리스트업</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -899,37 +890,37 @@
       <c r="G11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>W2 테스트 시작</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>★ 8/18 트랙 업로드 + 테스터 초대 발송</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>규희</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>★ 8/18 트랙 업로드 + 테스터 초대 발송 (콘솔)</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>하민</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>8/18</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>8/18</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>14일 시계 시작</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -939,7 +930,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>테스터 전원 설치(opt-in) 확인</t>
+          <t>테스터 전원 설치(opt-in) 확인 + 지역 데이터 시딩</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -954,7 +945,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8/20</t>
+          <t>8/24</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -975,7 +966,7 @@
           <t>전 여정 QA 1회전 (운영 DB·실데이터)</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>전원</t>
         </is>
@@ -1038,12 +1029,12 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>접수중 지역 운영 데이터 시딩</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>하민</t>
+          <t>제출 자료 초안 (소개서·시연 시나리오)</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>준서</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1058,7 +1049,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>지역 데이터</t>
+          <t>초안</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
@@ -1066,32 +1057,32 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>W2 테스트 시작</t>
+          <t>W3 안정화</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>제출 자료 초안 (소개서·시연 시나리오)</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>준서</t>
+          <t>QA 2회전 (엣지: 탈퇴·오프라인·권한거부)</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>전원</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>8/25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8/24</t>
+          <t>8/31</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>초안</t>
+          <t>QA 시트</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
@@ -1104,12 +1095,12 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>QA 2회전 (엣지: 탈퇴·오프라인·권한거부)</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>전원</t>
+          <t>취합 수정 (2차) + 빌드 n차 제작 → 하민 전달</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>규희</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1124,7 +1115,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>QA 시트</t>
+          <t>빌드 파일</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
@@ -1137,12 +1128,12 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>취합 수정 (2차) + 트랙 빌드 업데이트 (월·목)</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>규희</t>
+          <t>(콘솔) 트랙 빌드 업데이트(월·목) + 크래시 모니터링</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>하민</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1157,7 +1148,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>빌드 n차</t>
+          <t>빌드 반영</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
@@ -1229,37 +1220,37 @@
       <c r="G21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>W4 출시 신청</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>★ 9/1 프로덕션 액세스 신청 + 구글 심사 대응</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>규희</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>★ 9/1 프로덕션 액세스 신청 + 구글 심사 대응 (콘솔)</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>하민</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>9/1</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>9/7</t>
         </is>
       </c>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>심사 통과</t>
         </is>
       </c>
-      <c r="G22" s="8" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1269,12 +1260,12 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Render Starter 유료 전환 + 콜드스타트 확인</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>하민</t>
+          <t>최종 빌드 제작·전달 + 잔여 버그 수정</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>규희</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1289,7 +1280,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>상시 가동</t>
+          <t>최종 빌드</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
@@ -1302,12 +1293,12 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>출시 빌드 최종 QA</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>정훈</t>
+          <t>Render Starter 전환 + 콜드스타트 확인</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>하민</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1322,7 +1313,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>QA 통과</t>
+          <t>상시 가동</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
@@ -1335,63 +1326,63 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
+          <t>출시 빌드 최종 QA</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>정훈</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>9/1</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>9/7</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>QA 통과</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>W4 출시 신청</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
           <t>제출 자료 완성본 + 실데이터 스크린샷</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>준서</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>9/1</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>9/7</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>완성본</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>W5 정식 출시</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>★ 스토어 공개 확인 + Play앱서명 SHA-1 카카오 등록</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>규희</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>9/8</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>9/14</t>
-        </is>
-      </c>
-      <c r="F26" s="11" t="inlineStr">
-        <is>
-          <t>스토어판 소셜 OK</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1399,14 +1390,14 @@
           <t>W5 정식 출시</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>스토어 설치본 전 여정 최종 점검</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>전원</t>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>★ 스토어 공개 + Play앱서명 SHA-1 카카오 등록 (콘솔)</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>하민</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1421,7 +1412,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>점검 완료</t>
+          <t>스토어판 소셜 OK</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
@@ -1434,12 +1425,12 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>제출물에 스토어 URL 반영</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>준서</t>
+          <t>출시판 소셜 로그인 검증 + 잔여 수정</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>규희</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1454,7 +1445,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>URL 반영</t>
+          <t>검증 완료</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
@@ -1462,32 +1453,32 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>W6 공모전 제출</t>
+          <t>W5 정식 출시</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>제출물 완성(9/18) → 가제출 리허설</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>준서</t>
+          <t>스토어 설치본 전 여정 최종 점검</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>전원</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>9/8</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>9/14</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>리허설 OK</t>
+          <t>점검 완료</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
@@ -1495,32 +1486,32 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>W6 공모전 제출</t>
+          <t>W5 정식 출시</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>심사위원 테스트 계정 + TourAPI 실호출 최종 확인</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>규희</t>
+          <t>제출물에 스토어 URL 반영</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>준서</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>9/8</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>9/14</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>계정·호출 확인</t>
+          <t>URL 반영</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
@@ -1533,63 +1524,129 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
+          <t>제출물 완성(9/18) → 가제출 리허설</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>준서</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>리허설 OK</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>W6 공모전 제출</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>심사위원 테스트 계정 + TourAPI 실호출 최종 확인</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>규희</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>9/19</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>계정·호출 확인</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>W6 공모전 제출</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
           <t>서버 무중단 체제 확인 (심사 10월~10/28)</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>하민</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>9/15</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>9/21</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>모니터링</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>W6 공모전 제출</t>
         </is>
       </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>★ 9/21(월) 16:00 전 최종 제출</t>
         </is>
       </c>
-      <c r="C32" s="13" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>준서</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>9/21</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>9/21</t>
         </is>
       </c>
-      <c r="F32" s="11" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>제출 완료</t>
         </is>
       </c>
-      <c r="G32" s="8" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1602,17 +1659,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="44" customHeight="1">
@@ -1629,40 +1686,40 @@
       <c r="C1" s="1" t="inlineStr">
         <is>
           <t>W1
-8/14~8/17</t>
+8/14~17</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>W2
-8/18~8/24
-🚨테스트 시작</t>
+8/18~24
+🚨테스트</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>W3
-8/25~8/31</t>
+8/25~31</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>W4
-9/1~9/7
-출시 신청</t>
+9/1~7
+출시신청</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>W5
-9/8~9/14
-🚀정식 출시</t>
+9/8~14
+🚀출시</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>W6
-9/15~9/21
+9/15~21
 🏁제출</t>
         </is>
       </c>
@@ -1675,7 +1732,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>실서버 빌드 검증(로컬로그인)·키 투입·콘솔 세팅</t>
+          <t>실서버 빌드 검증 → AAB·자료 전달</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr"/>
@@ -1693,14 +1750,14 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>트랙 업로드 → QA 취합 수정 (메인 본체)</t>
+          <t>버그 픽스 전담 (QA 취합 수정, 빌드 제작→전달)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr"/>
       <c r="D3" s="5" t="inlineStr"/>
       <c r="E3" s="5" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
@@ -1711,50 +1768,50 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>프로덕션 신청·구글 심사 대응</t>
+          <t>심사위원 계정·TourAPI 최종 확인</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>규희</t>
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>정훈</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>출시 확정·카카오 Play서명 등록·최종 검증</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
+          <t>QA 총괄 — 시트 체계·회귀</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr"/>
+      <c r="D5" s="6" t="inlineStr"/>
+      <c r="E5" s="6" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>정훈</t>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>하민</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>QA 총괄 — 시트 체계·회귀 확인</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr"/>
-      <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="6" t="inlineStr"/>
+          <t>계정·키 발급·콘솔 세팅</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
@@ -1765,12 +1822,12 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>계정·키 발급·Render 확인</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="2" t="inlineStr"/>
+          <t>콘솔 운영(업로드·초대·모니터링)+데이터 시딩</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr"/>
@@ -1783,33 +1840,33 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>테스터 설치 관리·운영 데이터 시딩</t>
+          <t>프로덕션 신청·출시·Render 전환·무중단</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="4" t="inlineStr"/>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>하민</t>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>준서</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Render 유료 전환·무중단 운영</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr"/>
+          <t>제출물 파악·일러스트 리스트업</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -1819,13 +1876,13 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>제출물 파악·일러스트 리스트업</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr"/>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr"/>
+          <t>제출 자료 초안~완성·일러스트</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="7" t="inlineStr"/>
+      <c r="E10" s="7" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr"/>
     </row>
@@ -1837,51 +1894,33 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>제출 자료 초안~완성·일러스트 제작</t>
+          <t>URL 반영·리허설·최종 제출</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="7" t="inlineStr"/>
-      <c r="E11" s="7" t="inlineStr"/>
-      <c r="F11" s="7" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="7" t="inlineStr"/>
+      <c r="H11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>준서</t>
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>전원</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>스토어 URL 반영·리허설·최종 제출</t>
+          <t>실서버·실데이터 QA (전 여정)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr"/>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="7" t="inlineStr"/>
-      <c r="H12" s="7" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>전원</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>실서버·실데이터 QA (전 여정)</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr"/>
-      <c r="D13" s="12" t="inlineStr"/>
-      <c r="E13" s="12" t="inlineStr"/>
-      <c r="F13" s="12" t="inlineStr"/>
-      <c r="G13" s="12" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
+      <c r="D12" s="9" t="inlineStr"/>
+      <c r="E12" s="9" t="inlineStr"/>
+      <c r="F12" s="9" t="inlineStr"/>
+      <c r="G12" s="9" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1920,7 +1959,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>8/18(화)</t>
         </is>
@@ -1932,12 +1971,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>규희</t>
+          <t>하민</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>9/1(화)</t>
         </is>
@@ -1949,12 +1988,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>규희</t>
+          <t>하민</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>9/8~9/14</t>
         </is>
@@ -1966,12 +2005,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>규희</t>
+          <t>하민</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>9/18(금)</t>
         </is>
@@ -1988,7 +2027,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>9/21(월) 16:00</t>
         </is>
@@ -2005,7 +2044,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>10월~10/28</t>
         </is>
